--- a/ig/ch-vacd/StructureDefinition-ch-vacd-basic-immunization.xlsx
+++ b/ig/ch-vacd/StructureDefinition-ch-vacd-basic-immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T10:03:10+00:00</t>
+    <t>2026-06-11T13:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Condition to declare Basic Immunization done by one single condition for the declared vaccinations according to the ValueSet [Basic Immunization Codes](ValueSet-ch-vacd-basic-immunization-vs.html).  
+    <t>Condition to declare Basic Immunization done by one single condition for the declared vaccinations according to the ValueSet &lt;a href="ValueSet-ch-vacd-basic-immunization-vs.html"&gt;Basic Immunization Codes&lt;/a&gt;.  
 This is for cases the patient does not have a vaccination certificate to declare, but knows that it is done.</t>
   </si>
   <si>
